--- a/docs/plan-investissement-bot.xlsx
+++ b/docs/plan-investissement-bot.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Portefeuille final" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plan mensuel'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plan mensuel'!$A$1:$O$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ordre d''achat'!$A$1:$S$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Détail achats'!$A$1:$G$259</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Portefeuille final'!$A$1:$G$86</definedName>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>21402600</v>
+        <v>23046800</v>
       </c>
     </row>
     <row r="30">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="I3" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="13" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="K3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>10000</v>
+        <v>110000</v>
       </c>
       <c r="M3" s="13" t="n">
         <v>20</v>
@@ -1090,42 +1090,42 @@
         <v>5500</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>800</v>
+        <v>8800</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>780</v>
+        <v>8799</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Moneta Funded Instant-Direct 100k ×1</t>
+          <t>Moneta Funded Instant-Direct 100k ×11; FunderPro Futures 1 Step 150k ×1</t>
         </is>
       </c>
       <c r="I5" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>110000</v>
+        <v>1210000</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N5" s="13" t="n">
-        <v>1600</v>
+        <v>9600</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>1560</v>
+        <v>9579</v>
       </c>
     </row>
     <row r="6">
@@ -1133,39 +1133,35 @@
         <v>2.5</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>210000</v>
+        <v>1210000</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>10500</v>
+        <v>60500</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>8019</v>
+        <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Moneta Funded Instant-Direct 100k ×10; FunderPro Futures 1 Step 150k ×1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="inlineStr"/>
       <c r="I6" s="11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1150000</v>
+        <v>150000</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>210000</v>
+        <v>1210000</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>21</v>
@@ -1182,48 +1178,48 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>1210000</v>
+        <v>1360000</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>60500</v>
+        <v>68000</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>800</v>
+        <v>96800</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>780</v>
+        <v>96751</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Moneta Funded Instant-Direct 100k ×1</t>
+          <t>Moneta Funded Instant-Direct 100k ×11; IQ Capital Instant-Direct 100k ×20; Instant Funding Instant-Direct 120k ×3; Audacity Capital Instant-Direct 50k ×1; Crypto Fund Trader Instant-Direct 10k ×1</t>
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1360000</v>
+        <v>4880000</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>10400</v>
+        <v>106400</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>10359</v>
+        <v>106330</v>
       </c>
     </row>
     <row r="8">
@@ -1231,48 +1227,44 @@
         <v>3.5</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1460000</v>
+        <v>4880000</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>73000</v>
+        <v>244000</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>15988</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Moneta Funded Instant-Direct 100k ×10; IQ Capital Instant-Direct 100k ×2; Alpine Funded Instant-Direct 200k ×1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
       <c r="I8" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1460000</v>
+        <v>4880000</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>26400</v>
+        <v>106400</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>26347</v>
+        <v>106330</v>
       </c>
     </row>
     <row r="9">
@@ -1280,48 +1272,48 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>2860000</v>
+        <v>4880000</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>143000</v>
+        <v>244000</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>80800</v>
+        <v>387900</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>80706</v>
+        <v>387783</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>IQ Capital Instant-Direct 100k ×18; Instant Funding Instant-Direct 120k ×3; Audacity Capital Instant-Direct 50k ×1</t>
+          <t>Instant Funding Instant-Direct 120k ×5; Kickstart Trading Instant-Direct 100k ×10; Audacity Capital Instant-Direct 50k ×13; Fill88 Instant-Direct 100k ×6; Finotive Funding Instant-Direct 100k ×6; FNC Funding Instant-Direct 100k ×5; Funding Traders Instant-Direct 400k ×1; Ifunds Instant-Direct 500k ×1; Alpine Funded Instant-Direct 200k ×2; AquaFunded Instant-Direct 400k ×1; Atlas Funded Instant-Direct 300k ×1; Atmos Funded Instant-Direct 100k ×4; Blue Guardian Instant-Direct 400k ×1; FundedElite Instant-Direct 100k ×4; Funding Pips Instant-Direct 200k ×2; Global Forex Funds Instant-Direct 100k ×1; Goat Funded Trader Instant-Direct 100k ×4; FundedVerse Instant-Direct 50k ×6; Lark Funding Instant-Direct 100k ×3; Mockapital Instant-Direct 50k ×6; Myfundedcapital Instant-Direct 80k ×3; City Traders Imperium Instant-Direct 80k ×2; FTUK Instant-Direct 100k ×1; Funded Friday Instant-Direct 200k ×1; Funded Trading Plus Instant-Direct 100k ×1; Funding Dynasty Instant-Direct 200k ×1; Funding Frontier Instant-Direct 50k ×1; FundYourFX Instant-Direct 200k ×1; Hex Funded Instant-Direct 100k ×1; FundingRock Instant-Direct 100k ×1; LegionFunding Instant-Direct 100k ×1; MasterFunders Instant-Direct 100k ×1; BloomFunded Instant-Direct 50k ×1; BestProp4U 2 Step 400k ×2; Blink Funding 3 Step 500k ×2; Finotive Futures 1 Step 150k ×6; Funded Trader Markets 1 Step 300k ×3; Investiqa 2 Step 500k ×2; Kingdom Wealth Funding 1 Step 1000k ×1; Ment Funding 1 Step 1000k ×1; FXIFY 3 Step 400k ×2; Funded Squad 2 Step 200k ×4; Ment Funding Futures 1 Step 400k ×1; 10FOUR 1 Step 150k ×5; Blue Guardian Futures 1 Step 100k ×7; FunderPro Futures 1 Step 150k ×4; Fintokei 3 Step 100k ×7; DNA Funded 2 Step 200k ×3; Eightcap Challenges 2 Step 200k ×3; Capitalize 1 Step 500k ×1; E8 Markets 2 Step 150k ×3; Hola Prime 1 Step 150k ×3; IC Funded 2 Step 500k ×1; Blueberry Futures 1 Step 150k ×3; FTMO Futures 1 Step 150k ×3; Halcyon Trader Funding 1 Step 150k ×3; Astrofund 1 Step 100k ×4; BrightFunded 1 Step 200k ×2; Direct Funded Trader 2 Step 200k ×2; FTMO 1 Step 200k ×2; Funded X 1 Step 200k ×2; Hantec Trader 3 Step 200k ×1</t>
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>2210000</v>
+        <v>18000000</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2860000</v>
+        <v>15530000</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>107200</v>
+        <v>494300</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>107053</v>
+        <v>494113</v>
       </c>
     </row>
     <row r="10">
@@ -1329,48 +1321,44 @@
         <v>4.5</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>5070000</v>
+        <v>15530000</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>253500</v>
+        <v>776500</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>33144</v>
+        <v>0</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Instant Funding Instant-Direct 120k ×5; Kickstart Trading Instant-Direct 100k ×1; Atmos Funded Instant-Direct 100k ×1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
       <c r="I10" s="11" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>800000</v>
+        <v>18000000</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>5070000</v>
+        <v>15530000</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>140200</v>
+        <v>494300</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>140197</v>
+        <v>494113</v>
       </c>
     </row>
     <row r="11">
@@ -1378,48 +1366,48 @@
         <v>5</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>5870000</v>
+        <v>25230000</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>293500</v>
+        <v>1261500</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>196800</v>
+        <v>1300000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>196696</v>
+        <v>1299840</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Kickstart Trading Instant-Direct 100k ×9; Audacity Capital Instant-Direct 50k ×13; Fill88 Instant-Direct 100k ×6; Finotive Funding Instant-Direct 100k ×6; FNC Funding Instant-Direct 100k ×5; Funding Traders Instant-Direct 400k ×1; Ifunds Instant-Direct 500k ×1; Alpine Funded Instant-Direct 200k ×1; AquaFunded Instant-Direct 400k ×1; Atlas Funded Instant-Direct 300k ×1; Atmos Funded Instant-Direct 100k ×3; Blue Guardian Instant-Direct 400k ×1; FundedElite Instant-Direct 100k ×4; Funding Pips Instant-Direct 200k ×2; Global Forex Funds Instant-Direct 100k ×1; Goat Funded Trader Instant-Direct 100k ×4; FundedVerse Instant-Direct 50k ×6; Lark Funding Instant-Direct 100k ×1; Crypto Fund Trader Instant-Direct 10k ×1; Funding Frontier Instant-Direct 50k ×1; 10FOUR 1 Step 150k ×1</t>
+          <t>LifeUp Trading 1 Step 150k ×4; Fundora 2 Step 400k ×1; Get Crypto Funded 3 Step 200k ×2; Get Funded Now 1 Step 200k ×2; Hantec Trader 3 Step 200k ×1; Lion Heart Funding 2 Step 400k ×1; FX2 Funding 2 Step 100k ×3; FOREXIVE 2 Step 200k ×1; AIFO 2 Step 200k ×1; BEM Funding 2 Step 100k ×1; Breakout 1 Step 200k ×1; BullRush 2 Step 200k ×1; Exclusive Funded Programme 2 Step 200k ×1; FunderPro 1 Step 200k ×1; Funding Your Trades 2 Step 100k ×1; HyroTrader 1 Step 200k ×1; Mubite 2 Step 200k ×1; Tradersyard 1 Step 150k ×1</t>
         </is>
       </c>
       <c r="I11" s="14" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>7660000</v>
+        <v>12950000</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>5870000</v>
+        <v>25230000</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>107</v>
+        <v>347</v>
       </c>
       <c r="N11" s="13" t="n">
-        <v>337000</v>
+        <v>1794300</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>336893</v>
+        <v>1793953</v>
       </c>
     </row>
     <row r="12">
@@ -1427,48 +1415,44 @@
         <v>5.5</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>13380000</v>
+        <v>33330000</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>669000</v>
+        <v>1666500</v>
       </c>
       <c r="D12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>210300</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>177844</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>128</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Lark Funding Instant-Direct 100k ×2; Mockapital Instant-Direct 50k ×6; Myfundedcapital Instant-Direct 80k ×3; City Traders Imperium Instant-Direct 80k ×2; FTUK Instant-Direct 100k ×1; Funded Friday Instant-Direct 200k ×1; Funded Trading Plus Instant-Direct 100k ×1; Funding Dynasty Instant-Direct 200k ×1; FundYourFX Instant-Direct 200k ×1; Hex Funded Instant-Direct 100k ×1; FundingRock Instant-Direct 100k ×1; LegionFunding Instant-Direct 100k ×1; MasterFunders Instant-Direct 100k ×1; BloomFunded Instant-Direct 50k ×1; BestProp4U 2 Step 400k ×2; Blink Funding 3 Step 500k ×2; Finotive Futures 1 Step 150k ×6; Funded Trader Markets 1 Step 300k ×3; Investiqa 2 Step 500k ×2; Kingdom Wealth Funding 1 Step 1000k ×1; Ment Funding 1 Step 1000k ×1; FXIFY 3 Step 400k ×2; Funded Squad 2 Step 200k ×4; Ment Funding Futures 1 Step 400k ×1; 10FOUR 1 Step 150k ×4; Blue Guardian Futures 1 Step 100k ×7; FunderPro Futures 1 Step 150k ×4; Fintokei 3 Step 100k ×7; DNA Funded 2 Step 200k ×3; Eightcap Challenges 2 Step 200k ×3; Capitalize 1 Step 500k ×1; E8 Markets 2 Step 150k ×3; Hola Prime 1 Step 150k ×3; IC Funded 2 Step 500k ×1; Blueberry Futures 1 Step 150k ×3; FTMO Futures 1 Step 150k ×3; Halcyon Trader Funding 1 Step 150k ×3; Astrofund 1 Step 100k ×4; BrightFunded 1 Step 200k ×2; Direct Funded Trader 2 Step 200k ×2; FTMO 1 Step 200k ×2; Funded X 1 Step 200k ×2; Fundora 2 Step 400k ×1; Get Crypto Funded 3 Step 200k ×2; Get Funded Now 1 Step 200k ×2; Hantec Trader 3 Step 200k ×2; Lion Heart Funding 2 Step 400k ×1; FX2 Funding 2 Step 100k ×3; FOREXIVE 2 Step 200k ×1; AIFO 2 Step 200k ×1; BEM Funding 2 Step 100k ×1; Breakout 1 Step 200k ×1; BullRush 2 Step 200k ×1; Exclusive Funded Programme 2 Step 200k ×1; FunderPro 1 Step 200k ×1; Funding Your Trades 2 Step 100k ×1; HyroTrader 1 Step 200k ×1; Mubite 2 Step 200k ×1; Tradersyard 1 Step 150k ×1; MFunded (MarketsVox) 2 Step 100k ×1; Monevis 3 Step 100k ×1</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>129</v>
-      </c>
       <c r="J12" s="10" t="n">
-        <v>24400000</v>
+        <v>4850000</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>13530000</v>
+        <v>33330000</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>32563</v>
+        <v>347</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>547300</v>
+        <v>1794300</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>514737</v>
+        <v>1793953</v>
       </c>
     </row>
     <row r="13">
@@ -1476,44 +1460,48 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15680000</v>
+        <v>35280000</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>784000</v>
+        <v>1764000</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>261800</v>
+        <v>2125500</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0</v>
+        <v>320784</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>LifeUp Trading 1 Step 150k ×1; MFunded (MarketsVox) 2 Step 100k ×1; Monevis 3 Step 100k ×1</t>
+        </is>
+      </c>
       <c r="I13" s="14" t="n">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>22100000</v>
+        <v>3250000</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>26380000</v>
+        <v>35280000</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>294363</v>
+        <v>1805063</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>809100</v>
+        <v>3919800</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>514737</v>
+        <v>2114737</v>
       </c>
     </row>
     <row r="14">
@@ -1521,48 +1509,44 @@
         <v>6.5</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>26380000</v>
+        <v>37580000</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1319000</v>
+        <v>1879000</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>860100</v>
+        <v>680500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>960000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>LifeUp Trading 1 Step 150k ×3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
       <c r="I14" s="11" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>11850000</v>
+        <v>950000</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>36980000</v>
+        <v>37580000</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>194463</v>
+        <v>2485563</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>1669200</v>
+        <v>4600300</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>1474737</v>
+        <v>2114737</v>
       </c>
     </row>
     <row r="15">
@@ -1570,45 +1554,41 @@
         <v>7</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>36980000</v>
+        <v>38330000</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1849000</v>
+        <v>1916500</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>55</v>
+        <v>207</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>453400</v>
+        <v>2287500</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>640000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>LifeUp Trading 1 Step 150k ×2</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>9</v>
-      </c>
       <c r="J15" s="13" t="n">
-        <v>1550000</v>
+        <v>200000</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>38230000</v>
+        <v>38330000</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>7863</v>
+        <v>4773063</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>2122600</v>
+        <v>6887800</v>
       </c>
       <c r="O15" s="13" t="n">
         <v>2114737</v>
@@ -1619,16 +1599,16 @@
         <v>7.5</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>38230000</v>
+        <v>38530000</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1911500</v>
+        <v>1926500</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1767100</v>
+        <v>868500</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>0</v>
@@ -1638,22 +1618,22 @@
       </c>
       <c r="H16" s="11" t="inlineStr"/>
       <c r="I16" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>38530000</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>1774963</v>
+        <v>5641563</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>3889700</v>
+        <v>7756300</v>
       </c>
       <c r="O16" s="10" t="n">
         <v>2114737</v>
@@ -1670,10 +1650,10 @@
         <v>1926500</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1337900</v>
+        <v>2350500</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>0</v>
@@ -1695,10 +1675,10 @@
         <v>38530000</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>3112863</v>
+        <v>7992063</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>5227600</v>
+        <v>10106800</v>
       </c>
       <c r="O17" s="13" t="n">
         <v>2114737</v>
@@ -1715,10 +1695,10 @@
         <v>1926500</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1873100</v>
+        <v>884500</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>0</v>
@@ -1740,10 +1720,10 @@
         <v>38530000</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>4985963</v>
+        <v>8876563</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>7100700</v>
+        <v>10991300</v>
       </c>
       <c r="O18" s="10" t="n">
         <v>2114737</v>
@@ -1760,10 +1740,10 @@
         <v>1926500</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1361900</v>
+        <v>2350500</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>0</v>
@@ -1785,10 +1765,10 @@
         <v>38530000</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>6347863</v>
+        <v>11227063</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>8462600</v>
+        <v>13341800</v>
       </c>
       <c r="O19" s="13" t="n">
         <v>2114737</v>
@@ -1805,10 +1785,10 @@
         <v>1926500</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1873100</v>
+        <v>884500</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>0</v>
@@ -1830,10 +1810,10 @@
         <v>38530000</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>8220963</v>
+        <v>12111563</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>10335700</v>
+        <v>14226300</v>
       </c>
       <c r="O20" s="10" t="n">
         <v>2114737</v>
@@ -1850,10 +1830,10 @@
         <v>1926500</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1361900</v>
+        <v>2350500</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1875,10 +1855,10 @@
         <v>38530000</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>9582863</v>
+        <v>14462063</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>11697600</v>
+        <v>16576800</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>2114737</v>
@@ -1895,10 +1875,10 @@
         <v>1926500</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1873100</v>
+        <v>884500</v>
       </c>
       <c r="F22" s="10" t="n">
         <v>0</v>
@@ -1920,10 +1900,10 @@
         <v>38530000</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>11455963</v>
+        <v>15346563</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>13570700</v>
+        <v>17461300</v>
       </c>
       <c r="O22" s="10" t="n">
         <v>2114737</v>
@@ -1940,10 +1920,10 @@
         <v>1926500</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1361900</v>
+        <v>2350500</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>0</v>
@@ -1965,10 +1945,10 @@
         <v>38530000</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>12817863</v>
+        <v>17697063</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>14932600</v>
+        <v>19811800</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>2114737</v>
@@ -1985,10 +1965,10 @@
         <v>1926500</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1873100</v>
+        <v>884500</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>0</v>
@@ -2010,10 +1990,10 @@
         <v>38530000</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>14690963</v>
+        <v>18581563</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>16805700</v>
+        <v>20696300</v>
       </c>
       <c r="O24" s="10" t="n">
         <v>2114737</v>
@@ -2030,10 +2010,10 @@
         <v>1926500</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1361900</v>
+        <v>2350500</v>
       </c>
       <c r="F25" s="13" t="n">
         <v>0</v>
@@ -2055,107 +2035,17 @@
         <v>38530000</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>16052863</v>
+        <v>20932063</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>18167600</v>
+        <v>23046800</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>2114737</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>38530000</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>1926500</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>154</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1873100</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11" t="inlineStr"/>
-      <c r="I26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>259</v>
-      </c>
-      <c r="L26" s="9" t="n">
-        <v>38530000</v>
-      </c>
-      <c r="M26" s="10" t="n">
-        <v>17925963</v>
-      </c>
-      <c r="N26" s="10" t="n">
-        <v>20040700</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>2114737</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>38530000</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>1926500</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>105</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>1361900</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="14" t="inlineStr"/>
-      <c r="I27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="14" t="n">
-        <v>259</v>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>38530000</v>
-      </c>
-      <c r="M27" s="13" t="n">
-        <v>19287863</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>21402600</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>2114737</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O27"/>
+  <autoFilter ref="A1:O25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2352,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="S2" s="11" t="inlineStr">
         <is>
@@ -2422,10 +2312,10 @@
         <v>1</v>
       </c>
       <c r="Q3" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" s="14" t="inlineStr">
         <is>
@@ -2495,10 +2385,10 @@
         <v>1</v>
       </c>
       <c r="Q4" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
@@ -2568,10 +2458,10 @@
         <v>1</v>
       </c>
       <c r="Q5" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R5" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" s="14" t="inlineStr">
         <is>
@@ -2641,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="Q6" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
@@ -2714,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="Q7" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S7" s="14" t="inlineStr">
         <is>
@@ -2787,10 +2677,10 @@
         <v>1</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
@@ -2860,10 +2750,10 @@
         <v>1</v>
       </c>
       <c r="Q9" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S9" s="14" t="inlineStr">
         <is>
@@ -2933,10 +2823,10 @@
         <v>1</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
@@ -3006,10 +2896,10 @@
         <v>1</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11" s="14" t="inlineStr">
         <is>
@@ -3079,10 +2969,10 @@
         <v>1</v>
       </c>
       <c r="Q12" s="11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
@@ -3152,10 +3042,10 @@
         <v>1</v>
       </c>
       <c r="Q13" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R13" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S13" s="14" t="inlineStr">
         <is>
@@ -3225,10 +3115,10 @@
         <v>1</v>
       </c>
       <c r="Q14" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
@@ -3298,10 +3188,10 @@
         <v>1</v>
       </c>
       <c r="Q15" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
@@ -3371,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="Q16" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
@@ -3444,10 +3334,10 @@
         <v>1</v>
       </c>
       <c r="Q17" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
@@ -3517,10 +3407,10 @@
         <v>1</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
@@ -3590,10 +3480,10 @@
         <v>1</v>
       </c>
       <c r="Q19" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
@@ -3663,10 +3553,10 @@
         <v>1</v>
       </c>
       <c r="Q20" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S20" s="11" t="inlineStr">
         <is>
@@ -3736,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
@@ -3809,10 +3699,10 @@
         <v>1</v>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S22" s="11" t="inlineStr">
         <is>
@@ -3882,10 +3772,10 @@
         <v>1</v>
       </c>
       <c r="Q23" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R23" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
@@ -3955,10 +3845,10 @@
         <v>1</v>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S24" s="11" t="inlineStr">
         <is>
@@ -4028,10 +3918,10 @@
         <v>1</v>
       </c>
       <c r="Q25" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R25" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
@@ -4101,10 +3991,10 @@
         <v>1</v>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S26" s="11" t="inlineStr">
         <is>
@@ -4174,10 +4064,10 @@
         <v>1</v>
       </c>
       <c r="Q27" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R27" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
@@ -4247,10 +4137,10 @@
         <v>1</v>
       </c>
       <c r="Q28" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S28" s="11" t="inlineStr">
         <is>
@@ -4320,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R29" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
@@ -4393,10 +4283,10 @@
         <v>1</v>
       </c>
       <c r="Q30" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
@@ -4466,10 +4356,10 @@
         <v>1</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S31" s="14" t="inlineStr">
         <is>
@@ -4539,10 +4429,10 @@
         <v>1</v>
       </c>
       <c r="Q32" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S32" s="11" t="inlineStr">
         <is>
@@ -4612,10 +4502,10 @@
         <v>1</v>
       </c>
       <c r="Q33" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S33" s="14" t="inlineStr">
         <is>
@@ -4685,10 +4575,10 @@
         <v>1</v>
       </c>
       <c r="Q34" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
@@ -4758,10 +4648,10 @@
         <v>1</v>
       </c>
       <c r="Q35" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R35" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S35" s="14" t="inlineStr">
         <is>
@@ -4831,10 +4721,10 @@
         <v>1</v>
       </c>
       <c r="Q36" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R36" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S36" s="11" t="inlineStr">
         <is>
@@ -4904,10 +4794,10 @@
         <v>1</v>
       </c>
       <c r="Q37" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R37" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S37" s="14" t="inlineStr">
         <is>
@@ -4977,10 +4867,10 @@
         <v>1</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S38" s="11" t="inlineStr">
         <is>
@@ -5050,10 +4940,10 @@
         <v>1</v>
       </c>
       <c r="Q39" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R39" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S39" s="14" t="inlineStr">
         <is>
@@ -5123,10 +5013,10 @@
         <v>1</v>
       </c>
       <c r="Q40" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R40" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S40" s="11" t="inlineStr">
         <is>
@@ -5196,10 +5086,10 @@
         <v>1</v>
       </c>
       <c r="Q41" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R41" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S41" s="14" t="inlineStr">
         <is>
@@ -5269,10 +5159,10 @@
         <v>1</v>
       </c>
       <c r="Q42" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R42" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S42" s="11" t="inlineStr">
         <is>
@@ -5342,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="Q43" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R43" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S43" s="14" t="inlineStr">
         <is>
@@ -5415,10 +5305,10 @@
         <v>1</v>
       </c>
       <c r="Q44" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R44" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S44" s="11" t="inlineStr">
         <is>
@@ -5488,10 +5378,10 @@
         <v>1</v>
       </c>
       <c r="Q45" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R45" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S45" s="14" t="inlineStr">
         <is>
@@ -5561,10 +5451,10 @@
         <v>1</v>
       </c>
       <c r="Q46" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R46" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S46" s="11" t="inlineStr">
         <is>
@@ -5634,10 +5524,10 @@
         <v>1</v>
       </c>
       <c r="Q47" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R47" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S47" s="14" t="inlineStr">
         <is>
@@ -5707,10 +5597,10 @@
         <v>1</v>
       </c>
       <c r="Q48" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S48" s="11" t="inlineStr">
         <is>
@@ -5780,10 +5670,10 @@
         <v>1</v>
       </c>
       <c r="Q49" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R49" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S49" s="14" t="inlineStr">
         <is>
@@ -5853,10 +5743,10 @@
         <v>1</v>
       </c>
       <c r="Q50" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R50" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S50" s="11" t="inlineStr">
         <is>
@@ -5926,10 +5816,10 @@
         <v>1</v>
       </c>
       <c r="Q51" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R51" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S51" s="14" t="inlineStr">
         <is>
@@ -5999,10 +5889,10 @@
         <v>1</v>
       </c>
       <c r="Q52" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R52" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S52" s="11" t="inlineStr">
         <is>
@@ -6072,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="Q53" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R53" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S53" s="14" t="inlineStr">
         <is>
@@ -6145,10 +6035,10 @@
         <v>1</v>
       </c>
       <c r="Q54" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R54" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S54" s="11" t="inlineStr">
         <is>
@@ -6218,10 +6108,10 @@
         <v>1</v>
       </c>
       <c r="Q55" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R55" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S55" s="14" t="inlineStr">
         <is>
@@ -6291,10 +6181,10 @@
         <v>1</v>
       </c>
       <c r="Q56" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R56" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S56" s="11" t="inlineStr">
         <is>
@@ -6364,10 +6254,10 @@
         <v>1</v>
       </c>
       <c r="Q57" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R57" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S57" s="14" t="inlineStr">
         <is>
@@ -6437,10 +6327,10 @@
         <v>1</v>
       </c>
       <c r="Q58" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R58" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S58" s="11" t="inlineStr">
         <is>
@@ -6510,10 +6400,10 @@
         <v>1</v>
       </c>
       <c r="Q59" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R59" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S59" s="14" t="inlineStr">
         <is>
@@ -6583,10 +6473,10 @@
         <v>1</v>
       </c>
       <c r="Q60" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R60" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S60" s="11" t="inlineStr">
         <is>
@@ -6656,10 +6546,10 @@
         <v>1</v>
       </c>
       <c r="Q61" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R61" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S61" s="14" t="inlineStr">
         <is>
@@ -6729,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="Q62" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R62" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S62" s="11" t="inlineStr">
         <is>
@@ -6802,10 +6692,10 @@
         <v>1</v>
       </c>
       <c r="Q63" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R63" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S63" s="14" t="inlineStr">
         <is>
@@ -6875,10 +6765,10 @@
         <v>1</v>
       </c>
       <c r="Q64" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R64" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S64" s="11" t="inlineStr">
         <is>
@@ -6948,10 +6838,10 @@
         <v>1</v>
       </c>
       <c r="Q65" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R65" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S65" s="14" t="inlineStr">
         <is>
@@ -7021,10 +6911,10 @@
         <v>1</v>
       </c>
       <c r="Q66" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R66" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="S66" s="11" t="inlineStr">
         <is>
@@ -7094,10 +6984,10 @@
         <v>1</v>
       </c>
       <c r="Q67" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R67" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S67" s="14" t="inlineStr">
         <is>
@@ -7167,10 +7057,10 @@
         <v>1</v>
       </c>
       <c r="Q68" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R68" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S68" s="11" t="inlineStr">
         <is>
@@ -7240,10 +7130,10 @@
         <v>1</v>
       </c>
       <c r="Q69" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R69" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S69" s="14" t="inlineStr">
         <is>
@@ -7313,10 +7203,10 @@
         <v>1</v>
       </c>
       <c r="Q70" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R70" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S70" s="11" t="inlineStr">
         <is>
@@ -7386,10 +7276,10 @@
         <v>1</v>
       </c>
       <c r="Q71" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R71" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S71" s="14" t="inlineStr">
         <is>
@@ -7459,10 +7349,10 @@
         <v>1</v>
       </c>
       <c r="Q72" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R72" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S72" s="11" t="inlineStr">
         <is>
@@ -7532,10 +7422,10 @@
         <v>1</v>
       </c>
       <c r="Q73" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R73" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S73" s="14" t="inlineStr">
         <is>
@@ -7605,10 +7495,10 @@
         <v>1</v>
       </c>
       <c r="Q74" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R74" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S74" s="11" t="inlineStr">
         <is>
@@ -7678,10 +7568,10 @@
         <v>1</v>
       </c>
       <c r="Q75" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R75" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S75" s="14" t="inlineStr">
         <is>
@@ -7751,10 +7641,10 @@
         <v>1</v>
       </c>
       <c r="Q76" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R76" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S76" s="11" t="inlineStr">
         <is>
@@ -7824,10 +7714,10 @@
         <v>1</v>
       </c>
       <c r="Q77" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R77" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S77" s="14" t="inlineStr">
         <is>
@@ -7897,10 +7787,10 @@
         <v>1</v>
       </c>
       <c r="Q78" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R78" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S78" s="11" t="inlineStr">
         <is>
@@ -7970,10 +7860,10 @@
         <v>1</v>
       </c>
       <c r="Q79" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R79" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S79" s="14" t="inlineStr">
         <is>
@@ -8043,10 +7933,10 @@
         <v>1</v>
       </c>
       <c r="Q80" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R80" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S80" s="11" t="inlineStr">
         <is>
@@ -8116,10 +8006,10 @@
         <v>1</v>
       </c>
       <c r="Q81" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R81" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S81" s="14" t="inlineStr">
         <is>
@@ -8189,10 +8079,10 @@
         <v>1</v>
       </c>
       <c r="Q82" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R82" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S82" s="11" t="inlineStr">
         <is>
@@ -8262,10 +8152,10 @@
         <v>1</v>
       </c>
       <c r="Q83" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R83" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S83" s="14" t="inlineStr">
         <is>
@@ -8335,10 +8225,10 @@
         <v>1</v>
       </c>
       <c r="Q84" s="11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R84" s="11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="S84" s="11" t="inlineStr">
         <is>
@@ -8408,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="Q85" s="14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R85" s="14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="S85" s="14" t="inlineStr">
         <is>
@@ -8536,7 +8426,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
@@ -8555,15 +8445,15 @@
         <v>780</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
@@ -8582,15 +8472,15 @@
         <v>780</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
@@ -8609,15 +8499,15 @@
         <v>780</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
@@ -8636,15 +8526,15 @@
         <v>780</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
@@ -8663,15 +8553,15 @@
         <v>780</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
@@ -8690,15 +8580,15 @@
         <v>780</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
@@ -8717,15 +8607,15 @@
         <v>780</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
@@ -8744,15 +8634,15 @@
         <v>780</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
@@ -8771,15 +8661,15 @@
         <v>780</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
@@ -8798,15 +8688,15 @@
         <v>780</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
@@ -8825,10 +8715,10 @@
         <v>219</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -8860,7 +8750,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
@@ -8879,15 +8769,15 @@
         <v>780</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
@@ -8906,15 +8796,15 @@
         <v>780</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
@@ -8933,15 +8823,15 @@
         <v>780</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
@@ -8960,15 +8850,15 @@
         <v>780</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
@@ -8987,15 +8877,15 @@
         <v>780</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
@@ -9014,15 +8904,15 @@
         <v>780</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
@@ -9041,15 +8931,15 @@
         <v>780</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
@@ -9068,15 +8958,15 @@
         <v>780</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
@@ -9095,15 +8985,15 @@
         <v>780</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
@@ -9122,15 +9012,15 @@
         <v>780</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
@@ -9149,15 +9039,15 @@
         <v>3495</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
@@ -9176,19 +9066,19 @@
         <v>3495</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Alpine Funded</t>
+          <t>IQ Capital</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -9197,21 +9087,21 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1198</v>
+        <v>3495</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
@@ -9230,15 +9120,15 @@
         <v>3495</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
@@ -9257,15 +9147,15 @@
         <v>3495</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
@@ -9284,15 +9174,15 @@
         <v>3495</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
@@ -9311,15 +9201,15 @@
         <v>3495</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
@@ -9338,15 +9228,15 @@
         <v>3495</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
@@ -9365,15 +9255,15 @@
         <v>3495</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
@@ -9392,15 +9282,15 @@
         <v>3495</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
@@ -9419,15 +9309,15 @@
         <v>3495</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
@@ -9446,15 +9336,15 @@
         <v>3495</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
@@ -9473,15 +9363,15 @@
         <v>3495</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
@@ -9500,15 +9390,15 @@
         <v>3495</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
@@ -9527,15 +9417,15 @@
         <v>3495</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
@@ -9554,15 +9444,15 @@
         <v>3495</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
@@ -9581,15 +9471,15 @@
         <v>3495</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
@@ -9608,15 +9498,15 @@
         <v>3495</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
@@ -9635,15 +9525,15 @@
         <v>3495</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
@@ -9662,19 +9552,19 @@
         <v>3495</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>IQ Capital</t>
+          <t>Instant Funding</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -9683,21 +9573,21 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>3495</v>
+        <v>5499</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
@@ -9716,15 +9606,15 @@
         <v>5499</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
@@ -9743,19 +9633,19 @@
         <v>5499</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Instant Funding</t>
+          <t>Audacity Capital</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -9764,25 +9654,25 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>5499</v>
+        <v>1299</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Audacity Capital</t>
+          <t>Crypto Fund Trader</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -9791,21 +9681,21 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1299</v>
+        <v>475</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
@@ -9824,15 +9714,15 @@
         <v>5499</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
@@ -9851,15 +9741,15 @@
         <v>5499</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
@@ -9878,15 +9768,15 @@
         <v>5499</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
@@ -9905,15 +9795,15 @@
         <v>5499</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
@@ -9932,15 +9822,15 @@
         <v>5499</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
@@ -9959,19 +9849,19 @@
         <v>5000</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Atmos Funded</t>
+          <t>Kickstart Trading</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -9983,18 +9873,18 @@
         <v>100000</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>649</v>
+        <v>5000</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
@@ -10013,15 +9903,15 @@
         <v>5000</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
@@ -10040,15 +9930,15 @@
         <v>5000</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
@@ -10067,15 +9957,15 @@
         <v>5000</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
@@ -10094,15 +9984,15 @@
         <v>5000</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
@@ -10121,15 +10011,15 @@
         <v>5000</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
@@ -10148,15 +10038,15 @@
         <v>5000</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
@@ -10175,15 +10065,15 @@
         <v>5000</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
@@ -10202,19 +10092,19 @@
         <v>5000</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Kickstart Trading</t>
+          <t>Audacity Capital</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -10223,21 +10113,21 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>5000</v>
+        <v>1299</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
@@ -10256,15 +10146,15 @@
         <v>1299</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
@@ -10283,15 +10173,15 @@
         <v>1299</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
@@ -10310,15 +10200,15 @@
         <v>1299</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
@@ -10337,15 +10227,15 @@
         <v>1299</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
@@ -10364,15 +10254,15 @@
         <v>1299</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
@@ -10391,15 +10281,15 @@
         <v>1299</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
@@ -10418,15 +10308,15 @@
         <v>1299</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
@@ -10445,15 +10335,15 @@
         <v>1299</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
@@ -10472,15 +10362,15 @@
         <v>1299</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
@@ -10499,15 +10389,15 @@
         <v>1299</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
@@ -10526,15 +10416,15 @@
         <v>1299</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
@@ -10553,19 +10443,19 @@
         <v>1299</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Audacity Capital</t>
+          <t>Fill88</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
@@ -10574,21 +10464,21 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>1299</v>
+        <v>3699</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
@@ -10607,15 +10497,15 @@
         <v>3699</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
@@ -10634,15 +10524,15 @@
         <v>3699</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
@@ -10661,15 +10551,15 @@
         <v>3699</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
@@ -10688,15 +10578,15 @@
         <v>3699</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
@@ -10715,19 +10605,19 @@
         <v>3699</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Fill88</t>
+          <t>Finotive Funding</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
@@ -10739,18 +10629,18 @@
         <v>100000</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>3699</v>
+        <v>3549</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
@@ -10769,15 +10659,15 @@
         <v>3549</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
@@ -10796,15 +10686,15 @@
         <v>3549</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
@@ -10823,15 +10713,15 @@
         <v>3549</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
@@ -10850,15 +10740,15 @@
         <v>3549</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
@@ -10877,19 +10767,19 @@
         <v>3549</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Finotive Funding</t>
+          <t>FNC Funding</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
@@ -10901,18 +10791,18 @@
         <v>100000</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>3549</v>
+        <v>5000</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
@@ -10931,15 +10821,15 @@
         <v>5000</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
@@ -10958,15 +10848,15 @@
         <v>5000</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
@@ -10985,15 +10875,15 @@
         <v>5000</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
@@ -11012,19 +10902,19 @@
         <v>5000</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>FNC Funding</t>
+          <t>Funding Traders</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
@@ -11033,25 +10923,25 @@
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>5000</v>
+        <v>2349</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Funding Traders</t>
+          <t>Ifunds</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
@@ -11060,25 +10950,25 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>2349</v>
+        <v>30000</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>Ifunds</t>
+          <t>Alpine Funded</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
@@ -11087,21 +10977,21 @@
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>30000</v>
+        <v>1198</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
@@ -11120,15 +11010,15 @@
         <v>1198</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
@@ -11147,15 +11037,15 @@
         <v>2699</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
@@ -11174,15 +11064,15 @@
         <v>1598</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
@@ -11201,15 +11091,15 @@
         <v>649</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
@@ -11228,15 +11118,15 @@
         <v>649</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
@@ -11255,19 +11145,19 @@
         <v>649</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Blue Guardian</t>
+          <t>Atmos Funded</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
@@ -11276,25 +11166,25 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>2200</v>
+        <v>649</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>FundedElite</t>
+          <t>Blue Guardian</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
@@ -11303,21 +11193,21 @@
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>1489</v>
+        <v>2200</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
@@ -11336,15 +11226,15 @@
         <v>1489</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
@@ -11363,15 +11253,15 @@
         <v>1489</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
@@ -11390,19 +11280,19 @@
         <v>1489</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Funding Pips</t>
+          <t>FundedElite</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
@@ -11411,21 +11301,21 @@
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>888</v>
+        <v>1489</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
@@ -11444,19 +11334,19 @@
         <v>888</v>
       </c>
       <c r="F111" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Global Forex Funds</t>
+          <t>Funding Pips</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
@@ -11465,25 +11355,25 @@
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>2999</v>
+        <v>888</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>Goat Funded Trader</t>
+          <t>Global Forex Funds</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
@@ -11495,18 +11385,18 @@
         <v>100000</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>858</v>
+        <v>2999</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
@@ -11525,15 +11415,15 @@
         <v>858</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
@@ -11552,15 +11442,15 @@
         <v>858</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
@@ -11579,19 +11469,19 @@
         <v>858</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>FundedVerse</t>
+          <t>Goat Funded Trader</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
@@ -11600,21 +11490,21 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>699</v>
+        <v>858</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
@@ -11633,15 +11523,15 @@
         <v>699</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
@@ -11660,15 +11550,15 @@
         <v>699</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
@@ -11687,15 +11577,15 @@
         <v>699</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
@@ -11714,15 +11604,15 @@
         <v>699</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
@@ -11741,19 +11631,19 @@
         <v>699</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>Lark Funding</t>
+          <t>FundedVerse</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
@@ -11762,25 +11652,25 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>4500</v>
+        <v>699</v>
       </c>
       <c r="F123" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Crypto Fund Trader</t>
+          <t>Lark Funding</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -11789,25 +11679,25 @@
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>475</v>
+        <v>4500</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>Funding Frontier</t>
+          <t>Lark Funding</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
@@ -11816,52 +11706,52 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>749</v>
+        <v>4500</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>10FOUR</t>
+          <t>Lark Funding</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>Instant-Direct</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>248.57</v>
+        <v>4500</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>Lark Funding</t>
+          <t>Mockapital</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
@@ -11870,25 +11760,25 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Lark Funding</t>
+          <t>Mockapital</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
@@ -11897,21 +11787,21 @@
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
@@ -11930,15 +11820,15 @@
         <v>2250</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
@@ -11957,15 +11847,15 @@
         <v>2250</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
@@ -11984,15 +11874,15 @@
         <v>2250</v>
       </c>
       <c r="F131" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
@@ -12011,19 +11901,19 @@
         <v>2250</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B133" s="14" t="inlineStr">
         <is>
-          <t>Mockapital</t>
+          <t>Myfundedcapital</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
@@ -12032,25 +11922,25 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>2250</v>
+        <v>3470</v>
       </c>
       <c r="F133" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Mockapital</t>
+          <t>Myfundedcapital</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
@@ -12059,21 +11949,21 @@
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>2250</v>
+        <v>3470</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B135" s="14" t="inlineStr">
         <is>
@@ -12092,19 +11982,19 @@
         <v>3470</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Myfundedcapital</t>
+          <t>City Traders Imperium</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
@@ -12116,22 +12006,22 @@
         <v>80000</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>3470</v>
+        <v>1599</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B137" s="14" t="inlineStr">
         <is>
-          <t>Myfundedcapital</t>
+          <t>City Traders Imperium</t>
         </is>
       </c>
       <c r="C137" s="14" t="inlineStr">
@@ -12143,22 +12033,22 @@
         <v>80000</v>
       </c>
       <c r="E137" s="13" t="n">
-        <v>3470</v>
+        <v>1599</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>City Traders Imperium</t>
+          <t>FTUK</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
@@ -12167,25 +12057,25 @@
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>1599</v>
+        <v>1499</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B139" s="14" t="inlineStr">
         <is>
-          <t>City Traders Imperium</t>
+          <t>Funded Friday</t>
         </is>
       </c>
       <c r="C139" s="14" t="inlineStr">
@@ -12194,25 +12084,25 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="E139" s="13" t="n">
-        <v>1599</v>
+        <v>3899</v>
       </c>
       <c r="F139" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>FTUK</t>
+          <t>Funded Trading Plus</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
@@ -12224,22 +12114,22 @@
         <v>100000</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>1499</v>
+        <v>4499</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B141" s="14" t="inlineStr">
         <is>
-          <t>Funded Friday</t>
+          <t>Funding Dynasty</t>
         </is>
       </c>
       <c r="C141" s="14" t="inlineStr">
@@ -12251,22 +12141,22 @@
         <v>200000</v>
       </c>
       <c r="E141" s="13" t="n">
-        <v>3899</v>
+        <v>1656</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Funded Trading Plus</t>
+          <t>Funding Frontier</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
@@ -12275,25 +12165,25 @@
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>4499</v>
+        <v>749</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B143" s="14" t="inlineStr">
         <is>
-          <t>Funding Dynasty</t>
+          <t>FundYourFX</t>
         </is>
       </c>
       <c r="C143" s="14" t="inlineStr">
@@ -12305,22 +12195,22 @@
         <v>200000</v>
       </c>
       <c r="E143" s="13" t="n">
-        <v>1656</v>
+        <v>1599</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>FundYourFX</t>
+          <t>Hex Funded</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
@@ -12329,25 +12219,25 @@
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>1599</v>
+        <v>596</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B145" s="14" t="inlineStr">
         <is>
-          <t>Hex Funded</t>
+          <t>FundingRock</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
@@ -12359,22 +12249,22 @@
         <v>100000</v>
       </c>
       <c r="E145" s="13" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>FundingRock</t>
+          <t>LegionFunding</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
@@ -12386,22 +12276,22 @@
         <v>100000</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>600</v>
+        <v>699</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B147" s="14" t="inlineStr">
         <is>
-          <t>LegionFunding</t>
+          <t>MasterFunders</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
@@ -12413,22 +12303,22 @@
         <v>100000</v>
       </c>
       <c r="E147" s="13" t="n">
-        <v>699</v>
+        <v>4780</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>MasterFunders</t>
+          <t>BloomFunded</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
@@ -12437,37 +12327,37 @@
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>4780</v>
+        <v>680</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B149" s="14" t="inlineStr">
         <is>
-          <t>BloomFunded</t>
+          <t>BestProp4U</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>Instant-Direct</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="E149" s="13" t="n">
-        <v>680</v>
+        <v>2475</v>
       </c>
       <c r="F149" s="14" t="n">
         <v>5.5</v>
@@ -12478,7 +12368,7 @@
     </row>
     <row r="150">
       <c r="A150" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
@@ -12497,42 +12387,42 @@
         <v>2475</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>Blink Funding</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>3 Step</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E151" s="13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F151" s="14" t="n">
         <v>5.5</v>
       </c>
-      <c r="B151" s="14" t="inlineStr">
-        <is>
-          <t>BestProp4U</t>
-        </is>
-      </c>
-      <c r="C151" s="14" t="inlineStr">
-        <is>
-          <t>2 Step</t>
-        </is>
-      </c>
-      <c r="D151" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E151" s="13" t="n">
-        <v>2475</v>
-      </c>
-      <c r="F151" s="14" t="n">
-        <v>7</v>
-      </c>
       <c r="G151" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
@@ -12551,42 +12441,42 @@
         <v>1800</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B153" s="14" t="inlineStr">
         <is>
-          <t>Blink Funding</t>
+          <t>Finotive Futures</t>
         </is>
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>500000</v>
+        <v>150000</v>
       </c>
       <c r="E153" s="13" t="n">
-        <v>1800</v>
+        <v>399</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G153" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
@@ -12605,15 +12495,15 @@
         <v>399</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B155" s="14" t="inlineStr">
         <is>
@@ -12632,15 +12522,15 @@
         <v>399</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G155" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
@@ -12659,15 +12549,15 @@
         <v>399</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G156" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B157" s="14" t="inlineStr">
         <is>
@@ -12686,15 +12576,15 @@
         <v>399</v>
       </c>
       <c r="F157" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G157" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
@@ -12713,19 +12603,19 @@
         <v>399</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B159" s="14" t="inlineStr">
         <is>
-          <t>Finotive Futures</t>
+          <t>Funded Trader Markets</t>
         </is>
       </c>
       <c r="C159" s="14" t="inlineStr">
@@ -12734,21 +12624,21 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E159" s="13" t="n">
-        <v>399</v>
+        <v>1622</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G159" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
@@ -12767,15 +12657,15 @@
         <v>1622</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B161" s="14" t="inlineStr">
         <is>
@@ -12794,42 +12684,42 @@
         <v>1622</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G161" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>Investiqa</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>2 Step</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F162" s="11" t="n">
         <v>5.5</v>
       </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t>Funded Trader Markets</t>
-        </is>
-      </c>
-      <c r="C162" s="11" t="inlineStr">
-        <is>
-          <t>1 Step</t>
-        </is>
-      </c>
-      <c r="D162" s="10" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>1622</v>
-      </c>
-      <c r="F162" s="11" t="n">
+      <c r="G162" s="11" t="n">
         <v>6.5</v>
-      </c>
-      <c r="G162" s="11" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B163" s="14" t="inlineStr">
         <is>
@@ -12848,46 +12738,46 @@
         <v>2520</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G163" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Investiqa</t>
+          <t>Kingdom Wealth Funding</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>2520</v>
+        <v>8500</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G164" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B165" s="14" t="inlineStr">
         <is>
-          <t>Kingdom Wealth Funding</t>
+          <t>Ment Funding</t>
         </is>
       </c>
       <c r="C165" s="14" t="inlineStr">
@@ -12899,45 +12789,45 @@
         <v>1000000</v>
       </c>
       <c r="E165" s="13" t="n">
-        <v>8500</v>
+        <v>9750</v>
       </c>
       <c r="F165" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G165" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>FXIFY</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>3 Step</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F166" s="11" t="n">
         <v>5.5</v>
       </c>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t>Ment Funding</t>
-        </is>
-      </c>
-      <c r="C166" s="11" t="inlineStr">
-        <is>
-          <t>1 Step</t>
-        </is>
-      </c>
-      <c r="D166" s="10" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>9750</v>
-      </c>
-      <c r="F166" s="11" t="n">
+      <c r="G166" s="11" t="n">
         <v>6.5</v>
-      </c>
-      <c r="G166" s="11" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B167" s="14" t="inlineStr">
         <is>
@@ -12956,42 +12846,42 @@
         <v>1599</v>
       </c>
       <c r="F167" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G167" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>Funded Squad</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>2 Step</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F168" s="11" t="n">
         <v>5.5</v>
       </c>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>FXIFY</t>
-        </is>
-      </c>
-      <c r="C168" s="11" t="inlineStr">
-        <is>
-          <t>3 Step</t>
-        </is>
-      </c>
-      <c r="D168" s="10" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F168" s="11" t="n">
-        <v>7</v>
-      </c>
       <c r="G168" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B169" s="14" t="inlineStr">
         <is>
@@ -13010,15 +12900,15 @@
         <v>1199</v>
       </c>
       <c r="F169" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G169" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
@@ -13037,15 +12927,15 @@
         <v>1199</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G170" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B171" s="14" t="inlineStr">
         <is>
@@ -13064,46 +12954,46 @@
         <v>1199</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G171" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>Funded Squad</t>
+          <t>Ment Funding Futures</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1199</v>
+        <v>3900</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G172" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B173" s="14" t="inlineStr">
         <is>
-          <t>Ment Funding Futures</t>
+          <t>10FOUR</t>
         </is>
       </c>
       <c r="C173" s="14" t="inlineStr">
@@ -13112,21 +13002,21 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="E173" s="13" t="n">
-        <v>3900</v>
+        <v>248.57</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G173" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
@@ -13145,15 +13035,15 @@
         <v>248.57</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G174" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B175" s="14" t="inlineStr">
         <is>
@@ -13172,15 +13062,15 @@
         <v>248.57</v>
       </c>
       <c r="F175" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G175" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
@@ -13199,15 +13089,15 @@
         <v>248.57</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G176" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B177" s="14" t="inlineStr">
         <is>
@@ -13226,15 +13116,15 @@
         <v>248.57</v>
       </c>
       <c r="F177" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G177" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
@@ -13253,15 +13143,15 @@
         <v>2200</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G178" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B179" s="14" t="inlineStr">
         <is>
@@ -13280,15 +13170,15 @@
         <v>2200</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G179" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
@@ -13307,15 +13197,15 @@
         <v>2200</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G180" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B181" s="14" t="inlineStr">
         <is>
@@ -13334,15 +13224,15 @@
         <v>2200</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G181" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
@@ -13361,15 +13251,15 @@
         <v>2200</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G182" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B183" s="14" t="inlineStr">
         <is>
@@ -13388,15 +13278,15 @@
         <v>2200</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G183" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
@@ -13415,15 +13305,15 @@
         <v>2200</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G184" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B185" s="14" t="inlineStr">
         <is>
@@ -13442,15 +13332,15 @@
         <v>219</v>
       </c>
       <c r="F185" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G185" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
@@ -13469,15 +13359,15 @@
         <v>219</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G186" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B187" s="14" t="inlineStr">
         <is>
@@ -13496,15 +13386,15 @@
         <v>219</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G187" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
@@ -13523,15 +13413,15 @@
         <v>219</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G188" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B189" s="14" t="inlineStr">
         <is>
@@ -13550,15 +13440,15 @@
         <v>419</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G189" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
@@ -13577,15 +13467,15 @@
         <v>419</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G190" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B191" s="14" t="inlineStr">
         <is>
@@ -13604,15 +13494,15 @@
         <v>419</v>
       </c>
       <c r="F191" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G191" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
@@ -13631,15 +13521,15 @@
         <v>419</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G192" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B193" s="14" t="inlineStr">
         <is>
@@ -13658,15 +13548,15 @@
         <v>419</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G193" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
@@ -13685,15 +13575,15 @@
         <v>419</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G194" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B195" s="14" t="inlineStr">
         <is>
@@ -13712,15 +13602,15 @@
         <v>419</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G195" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
@@ -13739,15 +13629,15 @@
         <v>1079</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G196" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B197" s="14" t="inlineStr">
         <is>
@@ -13766,15 +13656,15 @@
         <v>1079</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G197" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
@@ -13793,15 +13683,15 @@
         <v>1079</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G198" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B199" s="14" t="inlineStr">
         <is>
@@ -13820,15 +13710,15 @@
         <v>1199</v>
       </c>
       <c r="F199" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G199" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
@@ -13847,15 +13737,15 @@
         <v>1199</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G200" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B201" s="14" t="inlineStr">
         <is>
@@ -13874,15 +13764,15 @@
         <v>1199</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G201" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
@@ -13901,15 +13791,15 @@
         <v>4999</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G202" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B203" s="14" t="inlineStr">
         <is>
@@ -13928,15 +13818,15 @@
         <v>390</v>
       </c>
       <c r="F203" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G203" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
@@ -13955,15 +13845,15 @@
         <v>390</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G204" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B205" s="14" t="inlineStr">
         <is>
@@ -13982,15 +13872,15 @@
         <v>390</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G205" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
@@ -14009,15 +13899,15 @@
         <v>359</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G206" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B207" s="14" t="inlineStr">
         <is>
@@ -14036,15 +13926,15 @@
         <v>359</v>
       </c>
       <c r="F207" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G207" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
@@ -14063,15 +13953,15 @@
         <v>359</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G208" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B209" s="14" t="inlineStr">
         <is>
@@ -14090,15 +13980,15 @@
         <v>2999</v>
       </c>
       <c r="F209" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G209" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
@@ -14117,15 +14007,15 @@
         <v>454</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G210" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B211" s="14" t="inlineStr">
         <is>
@@ -14144,15 +14034,15 @@
         <v>454</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G211" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
@@ -14171,15 +14061,15 @@
         <v>454</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G212" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B213" s="14" t="inlineStr">
         <is>
@@ -14198,15 +14088,15 @@
         <v>229</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G213" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
@@ -14225,15 +14115,15 @@
         <v>229</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G214" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B215" s="14" t="inlineStr">
         <is>
@@ -14252,15 +14142,15 @@
         <v>229</v>
       </c>
       <c r="F215" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G215" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
@@ -14279,15 +14169,15 @@
         <v>157</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G216" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B217" s="14" t="inlineStr">
         <is>
@@ -14306,15 +14196,15 @@
         <v>157</v>
       </c>
       <c r="F217" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G217" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
@@ -14333,15 +14223,15 @@
         <v>157</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G218" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B219" s="14" t="inlineStr">
         <is>
@@ -14360,15 +14250,15 @@
         <v>239</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G219" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
@@ -14387,15 +14277,15 @@
         <v>239</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G220" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B221" s="14" t="inlineStr">
         <is>
@@ -14414,15 +14304,15 @@
         <v>239</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G221" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
@@ -14441,15 +14331,15 @@
         <v>239</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G222" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B223" s="14" t="inlineStr">
         <is>
@@ -14468,15 +14358,15 @@
         <v>1032</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G223" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
@@ -14495,15 +14385,15 @@
         <v>1032</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G224" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B225" s="14" t="inlineStr">
         <is>
@@ -14522,15 +14412,15 @@
         <v>979</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G225" s="14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
@@ -14549,15 +14439,15 @@
         <v>979</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G226" s="11" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B227" s="14" t="inlineStr">
         <is>
@@ -14576,15 +14466,15 @@
         <v>1177</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G227" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
@@ -14603,15 +14493,15 @@
         <v>1177</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G228" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B229" s="14" t="inlineStr">
         <is>
@@ -14630,15 +14520,15 @@
         <v>989</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G229" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
@@ -14657,100 +14547,100 @@
         <v>989</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G230" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="14" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="B231" s="14" t="inlineStr">
         <is>
-          <t>Fundora</t>
+          <t>Hantec Trader</t>
         </is>
       </c>
       <c r="C231" s="14" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>3 Step</t>
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="E231" s="13" t="n">
-        <v>2133</v>
+        <v>499</v>
       </c>
       <c r="F231" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G231" s="14" t="n">
         <v>7</v>
-      </c>
-      <c r="G231" s="14" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>Get Crypto Funded</t>
+          <t>LifeUp Trading</t>
         </is>
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D232" s="10" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>899</v>
+        <v>320000</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G232" s="11" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B233" s="14" t="inlineStr">
         <is>
-          <t>Get Crypto Funded</t>
+          <t>LifeUp Trading</t>
         </is>
       </c>
       <c r="C233" s="14" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="E233" s="13" t="n">
-        <v>899</v>
+        <v>320000</v>
       </c>
       <c r="F233" s="14" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G233" s="14" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>Get Funded Now</t>
+          <t>LifeUp Trading</t>
         </is>
       </c>
       <c r="C234" s="11" t="inlineStr">
@@ -14759,25 +14649,25 @@
         </is>
       </c>
       <c r="D234" s="10" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>1345</v>
+        <v>320000</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G234" s="11" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B235" s="14" t="inlineStr">
         <is>
-          <t>Get Funded Now</t>
+          <t>LifeUp Trading</t>
         </is>
       </c>
       <c r="C235" s="14" t="inlineStr">
@@ -14786,52 +14676,52 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="E235" s="13" t="n">
-        <v>1345</v>
+        <v>320000</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G235" s="14" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>Hantec Trader</t>
+          <t>Fundora</t>
         </is>
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D236" s="10" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>499</v>
+        <v>2133</v>
       </c>
       <c r="F236" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G236" s="11" t="n">
         <v>7.5</v>
-      </c>
-      <c r="G236" s="11" t="n">
-        <v>8.5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B237" s="14" t="inlineStr">
         <is>
-          <t>Hantec Trader</t>
+          <t>Get Crypto Funded</t>
         </is>
       </c>
       <c r="C237" s="14" t="inlineStr">
@@ -14843,34 +14733,34 @@
         <v>200000</v>
       </c>
       <c r="E237" s="13" t="n">
-        <v>499</v>
+        <v>899</v>
       </c>
       <c r="F237" s="14" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G237" s="14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>Lion Heart Funding</t>
+          <t>Get Crypto Funded</t>
         </is>
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>3 Step</t>
         </is>
       </c>
       <c r="D238" s="10" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>1959</v>
+        <v>899</v>
       </c>
       <c r="F238" s="11" t="n">
         <v>7</v>
@@ -14881,77 +14771,77 @@
     </row>
     <row r="239">
       <c r="A239" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B239" s="14" t="inlineStr">
         <is>
-          <t>FX2 Funding</t>
+          <t>Get Funded Now</t>
         </is>
       </c>
       <c r="C239" s="14" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E239" s="13" t="n">
-        <v>550</v>
+        <v>1345</v>
       </c>
       <c r="F239" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G239" s="14" t="n">
         <v>7</v>
-      </c>
-      <c r="G239" s="14" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>FX2 Funding</t>
+          <t>Get Funded Now</t>
         </is>
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D240" s="10" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>550</v>
+        <v>1345</v>
       </c>
       <c r="F240" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G240" s="11" t="n">
         <v>7</v>
-      </c>
-      <c r="G240" s="11" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B241" s="14" t="inlineStr">
         <is>
-          <t>FX2 Funding</t>
+          <t>Hantec Trader</t>
         </is>
       </c>
       <c r="C241" s="14" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>3 Step</t>
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E241" s="13" t="n">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="F241" s="14" t="n">
         <v>7</v>
@@ -14962,11 +14852,11 @@
     </row>
     <row r="242">
       <c r="A242" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>FOREXIVE</t>
+          <t>Lion Heart Funding</t>
         </is>
       </c>
       <c r="C242" s="11" t="inlineStr">
@@ -14975,10 +14865,10 @@
         </is>
       </c>
       <c r="D242" s="10" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>999</v>
+        <v>1959</v>
       </c>
       <c r="F242" s="11" t="n">
         <v>6.5</v>
@@ -14989,11 +14879,11 @@
     </row>
     <row r="243">
       <c r="A243" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B243" s="14" t="inlineStr">
         <is>
-          <t>AIFO</t>
+          <t>FX2 Funding</t>
         </is>
       </c>
       <c r="C243" s="14" t="inlineStr">
@@ -15002,25 +14892,25 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E243" s="13" t="n">
-        <v>849</v>
+        <v>550</v>
       </c>
       <c r="F243" s="14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G243" s="14" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>BEM Funding</t>
+          <t>FX2 Funding</t>
         </is>
       </c>
       <c r="C244" s="11" t="inlineStr">
@@ -15032,34 +14922,34 @@
         <v>100000</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G244" s="11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B245" s="14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>FX2 Funding</t>
         </is>
       </c>
       <c r="C245" s="14" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E245" s="13" t="n">
-        <v>1090</v>
+        <v>550</v>
       </c>
       <c r="F245" s="14" t="n">
         <v>6.5</v>
@@ -15070,11 +14960,11 @@
     </row>
     <row r="246">
       <c r="A246" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>BullRush</t>
+          <t>FOREXIVE</t>
         </is>
       </c>
       <c r="C246" s="11" t="inlineStr">
@@ -15086,22 +14976,22 @@
         <v>200000</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>800</v>
+        <v>999</v>
       </c>
       <c r="F246" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G246" s="11" t="n">
         <v>7</v>
-      </c>
-      <c r="G246" s="11" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B247" s="14" t="inlineStr">
         <is>
-          <t>Exclusive Funded Programme</t>
+          <t>AIFO</t>
         </is>
       </c>
       <c r="C247" s="14" t="inlineStr">
@@ -15113,88 +15003,88 @@
         <v>200000</v>
       </c>
       <c r="E247" s="13" t="n">
-        <v>999</v>
+        <v>849</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G247" s="14" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>FunderPro</t>
+          <t>BEM Funding</t>
         </is>
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D248" s="10" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>989</v>
+        <v>519</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G248" s="11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B249" s="14" t="inlineStr">
         <is>
-          <t>Funding Your Trades</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="C249" s="14" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D249" s="13" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E249" s="13" t="n">
-        <v>459</v>
+        <v>1090</v>
       </c>
       <c r="F249" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G249" s="14" t="n">
         <v>7</v>
-      </c>
-      <c r="G249" s="14" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>HyroTrader</t>
+          <t>BullRush</t>
         </is>
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D250" s="10" t="n">
         <v>200000</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>969</v>
+        <v>800</v>
       </c>
       <c r="F250" s="11" t="n">
         <v>6.5</v>
@@ -15205,11 +15095,11 @@
     </row>
     <row r="251">
       <c r="A251" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B251" s="14" t="inlineStr">
         <is>
-          <t>Mubite</t>
+          <t>Exclusive Funded Programme</t>
         </is>
       </c>
       <c r="C251" s="14" t="inlineStr">
@@ -15221,22 +15111,22 @@
         <v>200000</v>
       </c>
       <c r="E251" s="13" t="n">
-        <v>1099</v>
+        <v>999</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G251" s="14" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>Tradersyard</t>
+          <t>FunderPro</t>
         </is>
       </c>
       <c r="C252" s="11" t="inlineStr">
@@ -15245,10 +15135,10 @@
         </is>
       </c>
       <c r="D252" s="10" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="E252" s="10" t="n">
-        <v>339</v>
+        <v>989</v>
       </c>
       <c r="F252" s="11" t="n">
         <v>6.5</v>
@@ -15259,11 +15149,11 @@
     </row>
     <row r="253">
       <c r="A253" s="14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B253" s="14" t="inlineStr">
         <is>
-          <t>MFunded (MarketsVox)</t>
+          <t>Funding Your Trades</t>
         </is>
       </c>
       <c r="C253" s="14" t="inlineStr">
@@ -15275,76 +15165,76 @@
         <v>100000</v>
       </c>
       <c r="E253" s="13" t="n">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G253" s="14" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="B254" s="11" t="inlineStr">
         <is>
-          <t>Monevis</t>
+          <t>HyroTrader</t>
         </is>
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="D254" s="10" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E254" s="10" t="n">
-        <v>385</v>
+        <v>969</v>
       </c>
       <c r="F254" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G254" s="11" t="n">
         <v>7</v>
-      </c>
-      <c r="G254" s="11" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B255" s="14" t="inlineStr">
+        <is>
+          <t>Mubite</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="inlineStr">
+        <is>
+          <t>2 Step</t>
+        </is>
+      </c>
+      <c r="D255" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E255" s="13" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F255" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="B255" s="14" t="inlineStr">
-        <is>
-          <t>LifeUp Trading</t>
-        </is>
-      </c>
-      <c r="C255" s="14" t="inlineStr">
-        <is>
-          <t>1 Step</t>
-        </is>
-      </c>
-      <c r="D255" s="13" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E255" s="13" t="n">
-        <v>320000</v>
-      </c>
-      <c r="F255" s="14" t="n">
+      <c r="G255" s="14" t="n">
         <v>7.5</v>
-      </c>
-      <c r="G255" s="14" t="n">
-        <v>8.5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="11" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="B256" s="11" t="inlineStr">
         <is>
-          <t>LifeUp Trading</t>
+          <t>Tradersyard</t>
         </is>
       </c>
       <c r="C256" s="11" t="inlineStr">
@@ -15356,18 +15246,18 @@
         <v>150000</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>320000</v>
+        <v>339</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G256" s="11" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="14" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="B257" s="14" t="inlineStr">
         <is>
@@ -15386,64 +15276,64 @@
         <v>320000</v>
       </c>
       <c r="F257" s="14" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G257" s="14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>LifeUp Trading</t>
+          <t>MFunded (MarketsVox)</t>
         </is>
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="D258" s="10" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E258" s="10" t="n">
-        <v>320000</v>
+        <v>399</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G258" s="11" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B259" s="14" t="inlineStr">
         <is>
-          <t>LifeUp Trading</t>
+          <t>Monevis</t>
         </is>
       </c>
       <c r="C259" s="14" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>3 Step</t>
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E259" s="13" t="n">
-        <v>320000</v>
+        <v>385</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G259" s="14" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -16374,7 +16264,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Alpine Funded</t>
+          <t>Funding Traders</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -16383,10 +16273,10 @@
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>400000</v>
@@ -16401,7 +16291,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Atmos Funded</t>
+          <t>Alpine Funded</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -16410,25 +16300,25 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>400000</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>36000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Funding Traders</t>
+          <t>AquaFunded</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -16446,16 +16336,16 @@
         <v>400000</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>40000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>AquaFunded</t>
+          <t>Atmos Funded</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -16464,10 +16354,10 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>400000</v>
@@ -16725,12 +16615,12 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Get Funded Now</t>
+          <t>Direct Funded Trader</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>1 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
@@ -16752,12 +16642,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>Direct Funded Trader</t>
+          <t>Hantec Trader</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>3 Step</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
@@ -16770,28 +16660,28 @@
         <v>400000</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>32000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Fundora</t>
+          <t>Get Funded Now</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>2 Step</t>
+          <t>1 Step</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>400000</v>
@@ -16806,7 +16696,7 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>Lion Heart Funding</t>
+          <t>Fundora</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -16833,19 +16723,19 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Get Crypto Funded</t>
+          <t>Lion Heart Funding</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>3 Step</t>
+          <t>2 Step</t>
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>400000</v>
@@ -16860,7 +16750,7 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>Hantec Trader</t>
+          <t>Get Crypto Funded</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -16878,10 +16768,10 @@
         <v>400000</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>38000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="53">
